--- a/results/final_N33_v5/Trend_Method_Comparison/Tables/Table_M3_Correction_Factor_Impact.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Tables/Table_M3_Correction_Factor_Impact.xlsx
@@ -545,19 +545,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.0037</v>
+        <v>1.0274</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.0439</v>
+        <v>1.3284</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>33.881</v>
+        <v>33.299</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>32.571</v>
+        <v>25.59</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -582,19 +582,19 @@
         <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1.0079</v>
+        <v>1.2591</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1.0333</v>
+        <v>2.7251</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>33.74</v>
+        <v>29.889</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>32.904</v>
+        <v>12.48</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>2</v>
@@ -616,22 +616,22 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.0109</v>
+        <v>1.0547</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.0984</v>
+        <v>1.6562</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>32.668</v>
+        <v>31.911</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>30.044</v>
+        <v>19.93</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>3</v>
